--- a/prueba02.xlsx
+++ b/prueba02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae46519d9f6f6d4/2025/Curso Oracle ONE/Hackaton/testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="11_AD4D2F04E46CFB4ACB3E20389D97F0C2683EDF16" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A70E627-26CE-44A1-9A80-A33F4CA76610}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="11_AD4D2F04E46CFB4ACB3E20389D97F0C2683EDF16" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2210952-0D3F-473E-B589-C4957282F11C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="16" r:id="rId1"/>
@@ -20,14 +20,10 @@
     <sheet name="vez" sheetId="6" r:id="rId5"/>
     <sheet name="mex" sheetId="8" r:id="rId6"/>
     <sheet name="esp" sheetId="9" r:id="rId7"/>
-    <sheet name="pos_fuerte" sheetId="3" r:id="rId8"/>
-    <sheet name="pos_leve" sheetId="4" r:id="rId9"/>
-    <sheet name="nega_fuerte" sheetId="10" r:id="rId10"/>
-    <sheet name="nega_leve" sheetId="11" r:id="rId11"/>
-    <sheet name="ironia_negativa" sheetId="12" r:id="rId12"/>
-    <sheet name="ironia_positiva" sheetId="15" r:id="rId13"/>
-    <sheet name="sarcasmo_negativo" sheetId="13" r:id="rId14"/>
-    <sheet name="sarcasmo_positivo" sheetId="14" r:id="rId15"/>
+    <sheet name="fuerte" sheetId="3" r:id="rId8"/>
+    <sheet name="leve" sheetId="4" r:id="rId9"/>
+    <sheet name="ironia" sheetId="12" r:id="rId10"/>
+    <sheet name="sarcasmo" sheetId="13" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -51,7 +47,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Prompt:
 Rol:
@@ -75,44 +71,8 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Cristi</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{9D2E1FB1-F520-4E41-982F-8B93DD53CF50}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Prompt:
-Rol:
-Eres un generador experto de comentarios irónicos para entrenamiento y evaluación de modelos de análisis de sentimientos.
-Tarea:
-Genera 100 comentarios con ironía clara, usando lenguaje informal típico de reseñas o redes sociales, sin modismos regionales.
-Ironía POSITIVA (negativa aparente → positiva real)
-El texto debe sonar negativo en la superficie
-El significado real debe expresar una experiencia positiva
-Usar queja irónica, crítica suave o expectativa baja
-Sentimiento real: POSITIVO
-Maximo 15 palabras
-Sin modismos
-Ejemplo válido:
-Qué desastre, funcionó todo perfecto.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2205" uniqueCount="2090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="2090">
   <si>
     <t>La experiencia estuvo bacán, todo funcionó impeque desde el primer minuto. El equipo súper buena onda, atentos y rápidos, así da gusto pagar por un servicio bien hecho.</t>
   </si>
@@ -6400,7 +6360,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -11128,2259 +11088,8 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A6096A0-26CC-48C5-9D76-95419E19EA10}">
-  <dimension ref="A1:C101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="185.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1106</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1115</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1121</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1123</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1135</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1146</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>1151</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1165</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="s">
-        <v>1190</v>
-      </c>
-      <c r="C86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90" t="s">
-        <v>1194</v>
-      </c>
-      <c r="C90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" t="s">
-        <v>1195</v>
-      </c>
-      <c r="C91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>91</v>
-      </c>
-      <c r="B92" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>92</v>
-      </c>
-      <c r="B93" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>93</v>
-      </c>
-      <c r="B94" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>94</v>
-      </c>
-      <c r="B95" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>95</v>
-      </c>
-      <c r="B96" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>96</v>
-      </c>
-      <c r="B97" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>98</v>
-      </c>
-      <c r="B99" t="s">
-        <v>1203</v>
-      </c>
-      <c r="C99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100" t="s">
-        <v>1204</v>
-      </c>
-      <c r="C100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>100</v>
-      </c>
-      <c r="B101" t="s">
-        <v>1205</v>
-      </c>
-      <c r="C101">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B200">
-    <sortCondition ref="B2:B200"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6561746F-0D8D-4073-8F18-CD1CF5C8E186}">
-  <dimension ref="A1:C101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="165.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1206</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1207</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1208</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1209</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1210</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1213</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1214</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1216</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1218</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1219</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1220</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1222</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1224</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1225</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1226</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1227</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1231</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1232</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1233</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1234</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1236</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1238</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1240</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1241</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1243</v>
-      </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1244</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1246</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>1248</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1249</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>1251</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1252</v>
-      </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1255</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1256</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1257</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1258</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1259</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1260</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1261</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1263</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1264</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="s">
-        <v>1267</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1269</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="s">
-        <v>1270</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="s">
-        <v>1271</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1273</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1275</v>
-      </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1276</v>
-      </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1277</v>
-      </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="s">
-        <v>1279</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1283</v>
-      </c>
-      <c r="C79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="s">
-        <v>1286</v>
-      </c>
-      <c r="C82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="s">
-        <v>1289</v>
-      </c>
-      <c r="C85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="s">
-        <v>1290</v>
-      </c>
-      <c r="C86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="s">
-        <v>1292</v>
-      </c>
-      <c r="C88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89" t="s">
-        <v>1293</v>
-      </c>
-      <c r="C89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>91</v>
-      </c>
-      <c r="B92" t="s">
-        <v>1296</v>
-      </c>
-      <c r="C92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>92</v>
-      </c>
-      <c r="B93" t="s">
-        <v>1297</v>
-      </c>
-      <c r="C93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>93</v>
-      </c>
-      <c r="B94" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>94</v>
-      </c>
-      <c r="B95" t="s">
-        <v>1299</v>
-      </c>
-      <c r="C95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>95</v>
-      </c>
-      <c r="B96" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>96</v>
-      </c>
-      <c r="B97" t="s">
-        <v>1301</v>
-      </c>
-      <c r="C97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98" t="s">
-        <v>1302</v>
-      </c>
-      <c r="C98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>98</v>
-      </c>
-      <c r="B99" t="s">
-        <v>1303</v>
-      </c>
-      <c r="C99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100" t="s">
-        <v>1304</v>
-      </c>
-      <c r="C100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>100</v>
-      </c>
-      <c r="B101" t="s">
-        <v>1305</v>
-      </c>
-      <c r="C101">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12847463-3E1C-439C-8B02-C83B0EEF73BB}">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="76.85546875" bestFit="1" customWidth="1"/>
@@ -14495,6 +12204,1106 @@
       </c>
       <c r="C101">
         <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>1</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>2</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>3</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>4</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>5</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>6</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>7</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>8</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>9</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>10</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>11</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>12</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>13</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>14</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>16</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>17</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>18</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>19</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>20</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>21</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>22</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>23</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>24</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>25</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>26</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>27</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>28</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>29</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>30</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>31</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>32</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>33</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>34</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>35</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>36</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>37</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>38</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>39</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>40</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>41</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>42</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>43</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>44</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>45</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>46</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>47</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>48</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>49</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>50</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>51</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>52</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>53</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>54</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>55</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>56</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>57</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>58</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>59</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>60</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>61</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>62</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>63</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>64</v>
+      </c>
+      <c r="B165" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>65</v>
+      </c>
+      <c r="B166" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>66</v>
+      </c>
+      <c r="B167" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>67</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>68</v>
+      </c>
+      <c r="B169" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>69</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>70</v>
+      </c>
+      <c r="B171" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>71</v>
+      </c>
+      <c r="B172" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>72</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>73</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>74</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>75</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>76</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>77</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>78</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>79</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>80</v>
+      </c>
+      <c r="B181" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>81</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>82</v>
+      </c>
+      <c r="B183" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>83</v>
+      </c>
+      <c r="B184" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>84</v>
+      </c>
+      <c r="B185" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>85</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>86</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>87</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>88</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>89</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>90</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>91</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>92</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>93</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>94</v>
+      </c>
+      <c r="B195" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>95</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>96</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>97</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>98</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>99</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>100</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C201">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -14506,1137 +13315,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89480DE6-3E31-4877-8F53-EF6791ED39F4}">
-  <dimension ref="A1:C101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1638</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1655</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1695</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1669</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1623</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1613</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1699</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1653</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1665</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1684</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1646</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1621</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1672</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1648</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1688</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1618</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1680</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1630</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1607</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1636</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1685</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1639</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1676</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1666</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1692</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1698</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1606</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1656</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1624</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1701</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1616</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1677</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1649</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1635</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1661</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1682</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1668</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1627</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1693</v>
-      </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1660</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>1697</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1632</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1687</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>1643</v>
-      </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1611</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1651</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1620</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1671</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1679</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1641</v>
-      </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1604</v>
-      </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1626</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1615</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1644</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1664</v>
-      </c>
-      <c r="C58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1683</v>
-      </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1702</v>
-      </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1659</v>
-      </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="s">
-        <v>1622</v>
-      </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="s">
-        <v>1650</v>
-      </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1696</v>
-      </c>
-      <c r="C64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1686</v>
-      </c>
-      <c r="C65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="s">
-        <v>1634</v>
-      </c>
-      <c r="C66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="s">
-        <v>1678</v>
-      </c>
-      <c r="C67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1670</v>
-      </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1694</v>
-      </c>
-      <c r="C69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1617</v>
-      </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1673</v>
-      </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1654</v>
-      </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1637</v>
-      </c>
-      <c r="C73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="s">
-        <v>1700</v>
-      </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1612</v>
-      </c>
-      <c r="C76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1652</v>
-      </c>
-      <c r="C77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1619</v>
-      </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1640</v>
-      </c>
-      <c r="C79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="s">
-        <v>1603</v>
-      </c>
-      <c r="C80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" t="s">
-        <v>1675</v>
-      </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="s">
-        <v>1689</v>
-      </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="s">
-        <v>1609</v>
-      </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="s">
-        <v>1629</v>
-      </c>
-      <c r="C86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87" t="s">
-        <v>1691</v>
-      </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="s">
-        <v>1662</v>
-      </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89" t="s">
-        <v>1681</v>
-      </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90" t="s">
-        <v>1642</v>
-      </c>
-      <c r="C90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" t="s">
-        <v>1667</v>
-      </c>
-      <c r="C91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>91</v>
-      </c>
-      <c r="B92" t="s">
-        <v>1625</v>
-      </c>
-      <c r="C92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>92</v>
-      </c>
-      <c r="B93" t="s">
-        <v>1674</v>
-      </c>
-      <c r="C93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>93</v>
-      </c>
-      <c r="B94" t="s">
-        <v>1645</v>
-      </c>
-      <c r="C94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>94</v>
-      </c>
-      <c r="B95" t="s">
-        <v>1690</v>
-      </c>
-      <c r="C95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>95</v>
-      </c>
-      <c r="B96" t="s">
-        <v>1663</v>
-      </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>96</v>
-      </c>
-      <c r="B97" t="s">
-        <v>1633</v>
-      </c>
-      <c r="C97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98" t="s">
-        <v>1610</v>
-      </c>
-      <c r="C98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>98</v>
-      </c>
-      <c r="B99" t="s">
-        <v>1614</v>
-      </c>
-      <c r="C99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100" t="s">
-        <v>1605</v>
-      </c>
-      <c r="C100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>100</v>
-      </c>
-      <c r="B101" t="s">
-        <v>1628</v>
-      </c>
-      <c r="C101">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B200">
-    <sortCondition ref="B2:B200"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8E9660-28AE-43E6-A571-CA8E72FA3848}">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="65.42578125" bestFit="1" customWidth="1"/>
@@ -16753,1130 +14434,1103 @@
         <v>0</v>
       </c>
     </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B200">
-    <sortCondition ref="B2:B200"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C44E523C-897B-4C92-BD03-BEF1861CAA61}">
-  <dimension ref="A1:C101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="64.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>1</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B103" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B104" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1429</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1412</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1441</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B105" t="s">
         <v>1464</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="C105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B106" t="s">
         <v>1455</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="C106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B107" t="s">
         <v>1486</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="C107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B108" t="s">
         <v>1479</v>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="C108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B109" t="s">
         <v>1421</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="C109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B110" t="s">
         <v>1459</v>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="C110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B111" t="s">
         <v>1431</v>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="C111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B112" t="s">
         <v>1416</v>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="C112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B113" t="s">
         <v>1469</v>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="C113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B114" t="s">
         <v>1447</v>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="C114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B115" t="s">
         <v>1408</v>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="C115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B116" t="s">
         <v>1454</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="C116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B117" t="s">
         <v>1477</v>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="C117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B118" t="s">
         <v>1410</v>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="C118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B119" t="s">
         <v>1432</v>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="C119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B120" t="s">
         <v>1491</v>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="C120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B121" t="s">
         <v>1446</v>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="C121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B122" t="s">
         <v>1468</v>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="C122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B123" t="s">
         <v>1420</v>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="C123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B124" t="s">
         <v>1473</v>
       </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="C124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B125" t="s">
         <v>1437</v>
       </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="C125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B126" t="s">
         <v>1437</v>
       </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="C126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B127" t="s">
         <v>1463</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="C127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B128" t="s">
         <v>1484</v>
       </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="C128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B129" t="s">
         <v>1472</v>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="C129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B130" t="s">
         <v>1423</v>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="C130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B131" t="s">
         <v>1417</v>
       </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="C131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B132" t="s">
         <v>1456</v>
       </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="C132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B133" t="s">
         <v>1434</v>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="C133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B134" t="s">
         <v>1409</v>
       </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="C134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B135" t="s">
         <v>1445</v>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="C135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B136" t="s">
         <v>1449</v>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37">
+      <c r="C136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B137" t="s">
         <v>1490</v>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="C137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B138" t="s">
         <v>1471</v>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39">
+      <c r="C138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B139" t="s">
         <v>1499</v>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40">
+      <c r="C139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B140" t="s">
         <v>1424</v>
       </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41">
+      <c r="C140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B141" t="s">
         <v>1428</v>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42">
+      <c r="C141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B142" t="s">
         <v>1461</v>
       </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="C142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B143" t="s">
         <v>1406</v>
       </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44">
+      <c r="C143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B144" t="s">
         <v>1453</v>
       </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="C144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B145" t="s">
         <v>1476</v>
       </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46">
+      <c r="C145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B146" t="s">
         <v>1458</v>
       </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47">
+      <c r="C146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B147" t="s">
         <v>1433</v>
       </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48">
+      <c r="C147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B148" t="s">
         <v>1494</v>
       </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49">
+      <c r="C148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B149" t="s">
         <v>1438</v>
       </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50">
+      <c r="C149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B150" t="s">
         <v>1502</v>
       </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51">
+      <c r="C150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B151" t="s">
         <v>1418</v>
       </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52">
+      <c r="C151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B152" t="s">
         <v>1444</v>
       </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53">
+      <c r="C152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B153" t="s">
         <v>1411</v>
       </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54">
+      <c r="C153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B154" t="s">
         <v>1483</v>
       </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55">
+      <c r="C154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B155" t="s">
         <v>1467</v>
       </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56">
+      <c r="C155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B156" t="s">
         <v>1495</v>
       </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57">
+      <c r="C156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B157" t="s">
         <v>1457</v>
       </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58">
+      <c r="C157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B158" t="s">
         <v>1419</v>
       </c>
-      <c r="C58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59">
+      <c r="C158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B159" t="s">
         <v>1492</v>
       </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60">
+      <c r="C159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B160" t="s">
         <v>1435</v>
       </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61">
+      <c r="C160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B161" t="s">
         <v>1475</v>
       </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62">
+      <c r="C161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B162" t="s">
         <v>1500</v>
       </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63">
+      <c r="C162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B163" t="s">
         <v>1478</v>
       </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64">
+      <c r="C163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B164" t="s">
         <v>1443</v>
       </c>
-      <c r="C64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65">
+      <c r="C164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B165" t="s">
         <v>1498</v>
       </c>
-      <c r="C65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66">
+      <c r="C165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B166" t="s">
         <v>1425</v>
       </c>
-      <c r="C66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67">
+      <c r="C166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B167" t="s">
         <v>1462</v>
       </c>
-      <c r="C67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68">
+      <c r="C167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B168" t="s">
         <v>1430</v>
       </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69">
+      <c r="C168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B169" t="s">
         <v>1470</v>
       </c>
-      <c r="C69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70">
+      <c r="C169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B170" t="s">
         <v>1415</v>
       </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71">
+      <c r="C170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B171" t="s">
         <v>1489</v>
       </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72">
+      <c r="C171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B172" t="s">
         <v>1452</v>
       </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73">
+      <c r="C172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173">
         <v>72</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B173" t="s">
         <v>1439</v>
       </c>
-      <c r="C73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74">
+      <c r="C173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B174" t="s">
         <v>1503</v>
       </c>
-      <c r="C74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75">
+      <c r="C174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B175" t="s">
         <v>1448</v>
       </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76">
+      <c r="C175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B176" t="s">
         <v>1485</v>
       </c>
-      <c r="C76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77">
+      <c r="C176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B177" t="s">
         <v>1482</v>
       </c>
-      <c r="C77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78">
+      <c r="C177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B178" t="s">
         <v>1466</v>
       </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79">
+      <c r="C178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B179" t="s">
         <v>1407</v>
       </c>
-      <c r="C79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80">
+      <c r="C179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B180" t="s">
         <v>1426</v>
       </c>
-      <c r="C80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81">
+      <c r="C180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B181" t="s">
         <v>1450</v>
       </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82">
+      <c r="C181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B182" t="s">
         <v>1480</v>
       </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83">
+      <c r="C182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B183" t="s">
         <v>1496</v>
       </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84">
+      <c r="C183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B184" t="s">
         <v>1504</v>
       </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85">
+      <c r="C184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B185" t="s">
         <v>1413</v>
       </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86">
+      <c r="C185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B186" t="s">
         <v>1440</v>
       </c>
-      <c r="C86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87">
+      <c r="C186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B187" t="s">
         <v>1487</v>
       </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88">
+      <c r="C187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B188" t="s">
         <v>1460</v>
       </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89">
+      <c r="C188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189">
         <v>88</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B189" t="s">
         <v>1422</v>
       </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90">
+      <c r="C189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190">
         <v>89</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B190" t="s">
         <v>1436</v>
       </c>
-      <c r="C90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91">
+      <c r="C190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191">
         <v>90</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B191" t="s">
         <v>1493</v>
       </c>
-      <c r="C91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92">
+      <c r="C191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B192" t="s">
         <v>1442</v>
       </c>
-      <c r="C92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93">
+      <c r="C192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193">
         <v>92</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B193" t="s">
         <v>1474</v>
       </c>
-      <c r="C93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94">
+      <c r="C193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194">
         <v>93</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B194" t="s">
         <v>1501</v>
       </c>
-      <c r="C94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95">
+      <c r="C194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195">
         <v>94</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B195" t="s">
         <v>1465</v>
       </c>
-      <c r="C95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96">
+      <c r="C195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196">
         <v>95</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B196" t="s">
         <v>1497</v>
       </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97">
+      <c r="C196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197">
         <v>96</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B197" t="s">
         <v>1427</v>
       </c>
-      <c r="C97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98">
+      <c r="C197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B198" t="s">
         <v>1414</v>
       </c>
-      <c r="C98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99">
+      <c r="C198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199">
         <v>98</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B199" t="s">
         <v>1481</v>
       </c>
-      <c r="C99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100">
+      <c r="C199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B200" t="s">
         <v>1451</v>
       </c>
-      <c r="C100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101">
+      <c r="C200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B201" t="s">
         <v>1488</v>
       </c>
-      <c r="C101">
+      <c r="C201">
         <v>1</v>
       </c>
     </row>
@@ -28614,7 +26268,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DFE9A4-A101-4B12-942C-A56A26954F91}">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="150.85546875" bestFit="1" customWidth="1"/>
@@ -29729,6 +27383,1106 @@
       </c>
       <c r="C101">
         <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>1</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>2</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>3</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>4</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>5</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>6</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>7</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>8</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>9</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>10</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>11</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>12</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>13</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>14</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>16</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>17</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>18</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>19</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>20</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>21</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>22</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>23</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>24</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>25</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>26</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>27</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>28</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>29</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>30</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>31</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>32</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>33</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>34</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>35</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>36</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>37</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>38</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>39</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>40</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>41</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>42</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>43</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>44</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>45</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>46</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>47</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>48</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>49</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>50</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>51</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>52</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>53</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>54</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>55</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>56</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>57</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>58</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>59</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>60</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>61</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>62</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>63</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>64</v>
+      </c>
+      <c r="B165" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>65</v>
+      </c>
+      <c r="B166" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>66</v>
+      </c>
+      <c r="B167" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>67</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>68</v>
+      </c>
+      <c r="B169" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>69</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>70</v>
+      </c>
+      <c r="B171" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>71</v>
+      </c>
+      <c r="B172" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>72</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>73</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>74</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>75</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>76</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>77</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>78</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>79</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>80</v>
+      </c>
+      <c r="B181" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>81</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>82</v>
+      </c>
+      <c r="B183" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>83</v>
+      </c>
+      <c r="B184" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>84</v>
+      </c>
+      <c r="B185" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>85</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>86</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>87</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>88</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>89</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>90</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>91</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>92</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>93</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>94</v>
+      </c>
+      <c r="B195" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>95</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>96</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>97</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>98</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>99</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>100</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -29741,7 +28495,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD3E71D2-5AF9-40E4-AE77-034380F59047}">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="156.42578125" bestFit="1" customWidth="1"/>
@@ -30858,6 +29612,1106 @@
         <v>1</v>
       </c>
     </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>1</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>2</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>3</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>4</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>5</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>6</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>7</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>8</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>9</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>10</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>11</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>12</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>13</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>14</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>16</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>17</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>18</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>19</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>20</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>21</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>22</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>23</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>24</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>25</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>26</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>27</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>28</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>29</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>30</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>31</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>32</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>33</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>34</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>35</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>36</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>37</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>38</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>39</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>40</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>41</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>42</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>43</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>44</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>45</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>46</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>47</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>48</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>49</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>50</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>51</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>52</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>53</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>54</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>55</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>56</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>57</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>58</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>59</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>60</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>61</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>62</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>63</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>64</v>
+      </c>
+      <c r="B165" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>65</v>
+      </c>
+      <c r="B166" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>66</v>
+      </c>
+      <c r="B167" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>67</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>68</v>
+      </c>
+      <c r="B169" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>69</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>70</v>
+      </c>
+      <c r="B171" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>71</v>
+      </c>
+      <c r="B172" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>72</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>73</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>74</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>75</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>76</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>77</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>78</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>79</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>80</v>
+      </c>
+      <c r="B181" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>81</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>82</v>
+      </c>
+      <c r="B183" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>83</v>
+      </c>
+      <c r="B184" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>84</v>
+      </c>
+      <c r="B185" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>85</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>86</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>87</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>88</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>89</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>90</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>91</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>92</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>93</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>94</v>
+      </c>
+      <c r="B195" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>95</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>96</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>97</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>98</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>99</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>100</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B200">
     <sortCondition ref="B2:B200"/>
